--- a/output/yearly_population_iteration_37_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_37_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6715</v>
+        <v>6173</v>
       </c>
       <c r="C2" t="n">
-        <v>13104</v>
+        <v>7404</v>
       </c>
       <c r="D2" t="n">
-        <v>29492</v>
+        <v>26782</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3441</v>
+        <v>3917</v>
       </c>
       <c r="C3" t="n">
-        <v>8138</v>
+        <v>6069</v>
       </c>
       <c r="D3" t="n">
-        <v>13931</v>
+        <v>15095</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2519</v>
+        <v>3092</v>
       </c>
       <c r="C4" t="n">
-        <v>7443</v>
+        <v>5203</v>
       </c>
       <c r="D4" t="n">
-        <v>5350</v>
+        <v>7403</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1654</v>
+        <v>1776</v>
       </c>
       <c r="C5" t="n">
-        <v>5235</v>
+        <v>4385</v>
       </c>
       <c r="D5" t="n">
-        <v>2003</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>904</v>
+        <v>883</v>
       </c>
       <c r="C6" t="n">
-        <v>3280</v>
+        <v>3012</v>
       </c>
       <c r="D6" t="n">
-        <v>963</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="C7" t="n">
-        <v>2143</v>
+        <v>1848</v>
       </c>
       <c r="D7" t="n">
-        <v>624</v>
+        <v>652</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C8" t="n">
-        <v>1097</v>
+        <v>870</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>457</v>
+        <v>348</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5691</v>
+        <v>5986</v>
       </c>
       <c r="C2" t="n">
-        <v>10446</v>
+        <v>12176</v>
       </c>
       <c r="D2" t="n">
-        <v>25651</v>
+        <v>24594</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3932</v>
+        <v>4009</v>
       </c>
       <c r="C3" t="n">
-        <v>9121</v>
+        <v>5874</v>
       </c>
       <c r="D3" t="n">
-        <v>15111</v>
+        <v>15670</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2511</v>
+        <v>2982</v>
       </c>
       <c r="C4" t="n">
-        <v>7615</v>
+        <v>5510</v>
       </c>
       <c r="D4" t="n">
-        <v>6587</v>
+        <v>8433</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1784</v>
+        <v>2054</v>
       </c>
       <c r="C5" t="n">
-        <v>6072</v>
+        <v>4628</v>
       </c>
       <c r="D5" t="n">
-        <v>2436</v>
+        <v>3435</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1106</v>
+        <v>1145</v>
       </c>
       <c r="C6" t="n">
-        <v>4111</v>
+        <v>3601</v>
       </c>
       <c r="D6" t="n">
-        <v>1109</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="C7" t="n">
-        <v>2611</v>
+        <v>2342</v>
       </c>
       <c r="D7" t="n">
-        <v>661</v>
+        <v>713</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C8" t="n">
-        <v>1526</v>
+        <v>1291</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9" t="n">
-        <v>720</v>
+        <v>559</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>313</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
         <v>164</v>
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5776</v>
+        <v>7503</v>
       </c>
       <c r="C2" t="n">
-        <v>12216</v>
+        <v>10145</v>
       </c>
       <c r="D2" t="n">
-        <v>30219</v>
+        <v>29327</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3795</v>
+        <v>3937</v>
       </c>
       <c r="C3" t="n">
-        <v>8580</v>
+        <v>7525</v>
       </c>
       <c r="D3" t="n">
-        <v>15408</v>
+        <v>15934</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2608</v>
+        <v>2898</v>
       </c>
       <c r="C4" t="n">
-        <v>8019</v>
+        <v>5556</v>
       </c>
       <c r="D4" t="n">
-        <v>7550</v>
+        <v>9137</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1858</v>
+        <v>2154</v>
       </c>
       <c r="C5" t="n">
-        <v>6524</v>
+        <v>4859</v>
       </c>
       <c r="D5" t="n">
-        <v>2959</v>
+        <v>4017</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1245</v>
+        <v>1381</v>
       </c>
       <c r="C6" t="n">
-        <v>4865</v>
+        <v>3992</v>
       </c>
       <c r="D6" t="n">
-        <v>1262</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>686</v>
+        <v>700</v>
       </c>
       <c r="C7" t="n">
-        <v>3172</v>
+        <v>2823</v>
       </c>
       <c r="D7" t="n">
-        <v>715</v>
+        <v>793</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C8" t="n">
-        <v>1925</v>
+        <v>1689</v>
       </c>
       <c r="D8" t="n">
-        <v>473</v>
+        <v>489</v>
       </c>
     </row>
     <row r="9">
@@ -1503,7 +1503,7 @@
         <v>124</v>
       </c>
       <c r="C9" t="n">
-        <v>1019</v>
+        <v>838</v>
       </c>
       <c r="D9" t="n">
         <v>331</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>453</v>
+        <v>368</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
         <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5500</v>
+        <v>6883</v>
       </c>
       <c r="C2" t="n">
-        <v>8502</v>
+        <v>6898</v>
       </c>
       <c r="D2" t="n">
-        <v>24914</v>
+        <v>24073</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4582</v>
+        <v>4951</v>
       </c>
       <c r="C3" t="n">
-        <v>12894</v>
+        <v>10734</v>
       </c>
       <c r="D3" t="n">
-        <v>16371</v>
+        <v>17491</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1716</v>
+        <v>1990</v>
       </c>
       <c r="C4" t="n">
-        <v>10574</v>
+        <v>7704</v>
       </c>
       <c r="D4" t="n">
-        <v>6973</v>
+        <v>8741</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1150</v>
+        <v>1276</v>
       </c>
       <c r="C5" t="n">
-        <v>4767</v>
+        <v>3912</v>
       </c>
       <c r="D5" t="n">
-        <v>2032</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>633</v>
+        <v>646</v>
       </c>
       <c r="C6" t="n">
-        <v>3108</v>
+        <v>2766</v>
       </c>
       <c r="D6" t="n">
-        <v>700</v>
+        <v>777</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C7" t="n">
-        <v>1886</v>
+        <v>1655</v>
       </c>
       <c r="D7" t="n">
-        <v>463</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8">
@@ -1800,7 +1800,7 @@
         <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>998</v>
+        <v>821</v>
       </c>
       <c r="D8" t="n">
         <v>324</v>
@@ -1814,10 +1814,10 @@
         <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>443</v>
+        <v>360</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
         <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
         <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3545</v>
+        <v>4146</v>
       </c>
       <c r="C2" t="n">
-        <v>4287</v>
+        <v>3278</v>
       </c>
       <c r="D2" t="n">
-        <v>17567</v>
+        <v>16520</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4331</v>
+        <v>4986</v>
       </c>
       <c r="C3" t="n">
-        <v>9961</v>
+        <v>8172</v>
       </c>
       <c r="D3" t="n">
-        <v>16747</v>
+        <v>17378</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2399</v>
+        <v>2705</v>
       </c>
       <c r="C4" t="n">
-        <v>11705</v>
+        <v>9161</v>
       </c>
       <c r="D4" t="n">
-        <v>8181</v>
+        <v>9987</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1285</v>
+        <v>1449</v>
       </c>
       <c r="C5" t="n">
-        <v>7238</v>
+        <v>5583</v>
       </c>
       <c r="D5" t="n">
-        <v>2645</v>
+        <v>3443</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>744</v>
+        <v>779</v>
       </c>
       <c r="C6" t="n">
-        <v>3855</v>
+        <v>3303</v>
       </c>
       <c r="D6" t="n">
-        <v>827</v>
+        <v>977</v>
       </c>
     </row>
     <row r="7">
@@ -2097,10 +2097,10 @@
         <v>272</v>
       </c>
       <c r="C7" t="n">
-        <v>2344</v>
+        <v>2105</v>
       </c>
       <c r="D7" t="n">
-        <v>500</v>
+        <v>523</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C8" t="n">
-        <v>1293</v>
+        <v>1080</v>
       </c>
       <c r="D8" t="n">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>478</v>
+        <v>408</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3932</v>
+        <v>4054</v>
       </c>
       <c r="C2" t="n">
-        <v>9175</v>
+        <v>4650</v>
       </c>
       <c r="D2" t="n">
-        <v>19467</v>
+        <v>21402</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3376</v>
+        <v>3932</v>
       </c>
       <c r="C3" t="n">
-        <v>6496</v>
+        <v>5207</v>
       </c>
       <c r="D3" t="n">
-        <v>15733</v>
+        <v>16093</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2743</v>
+        <v>3147</v>
       </c>
       <c r="C4" t="n">
-        <v>10736</v>
+        <v>8486</v>
       </c>
       <c r="D4" t="n">
-        <v>9330</v>
+        <v>10889</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1548</v>
+        <v>1755</v>
       </c>
       <c r="C5" t="n">
-        <v>9102</v>
+        <v>7149</v>
       </c>
       <c r="D5" t="n">
-        <v>3414</v>
+        <v>4343</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>889</v>
+        <v>971</v>
       </c>
       <c r="C6" t="n">
-        <v>5280</v>
+        <v>4331</v>
       </c>
       <c r="D6" t="n">
-        <v>1077</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="C7" t="n">
-        <v>3002</v>
+        <v>2641</v>
       </c>
       <c r="D7" t="n">
-        <v>539</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C8" t="n">
-        <v>1717</v>
+        <v>1501</v>
       </c>
       <c r="D8" t="n">
-        <v>350</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>778</v>
+        <v>662</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>322</v>
+        <v>292</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2537,7 +2537,7 @@
         <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2381</v>
+        <v>2417</v>
       </c>
       <c r="C2" t="n">
-        <v>4461</v>
+        <v>2179</v>
       </c>
       <c r="D2" t="n">
-        <v>13616</v>
+        <v>14951</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3380</v>
+        <v>3855</v>
       </c>
       <c r="C3" t="n">
-        <v>7176</v>
+        <v>4861</v>
       </c>
       <c r="D3" t="n">
-        <v>15768</v>
+        <v>16284</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2996</v>
+        <v>3441</v>
       </c>
       <c r="C4" t="n">
-        <v>10240</v>
+        <v>8053</v>
       </c>
       <c r="D4" t="n">
-        <v>10080</v>
+        <v>11571</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1592</v>
+        <v>1799</v>
       </c>
       <c r="C5" t="n">
-        <v>10811</v>
+        <v>8566</v>
       </c>
       <c r="D5" t="n">
-        <v>3629</v>
+        <v>4583</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>709</v>
+        <v>771</v>
       </c>
       <c r="C6" t="n">
-        <v>6161</v>
+        <v>5161</v>
       </c>
       <c r="D6" t="n">
-        <v>1071</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C7" t="n">
-        <v>3119</v>
+        <v>2774</v>
       </c>
       <c r="D7" t="n">
-        <v>547</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>1267</v>
+        <v>1104</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>315</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2834,7 +2834,7 @@
         <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3271</v>
+        <v>2655</v>
       </c>
       <c r="C2" t="n">
-        <v>7732</v>
+        <v>4571</v>
       </c>
       <c r="D2" t="n">
-        <v>15606</v>
+        <v>16595</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2528</v>
+        <v>2796</v>
       </c>
       <c r="C3" t="n">
-        <v>5364</v>
+        <v>3251</v>
       </c>
       <c r="D3" t="n">
-        <v>14458</v>
+        <v>15164</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2779</v>
+        <v>3157</v>
       </c>
       <c r="C4" t="n">
-        <v>8644</v>
+        <v>6383</v>
       </c>
       <c r="D4" t="n">
-        <v>10647</v>
+        <v>11943</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1897</v>
+        <v>2185</v>
       </c>
       <c r="C5" t="n">
-        <v>10443</v>
+        <v>8238</v>
       </c>
       <c r="D5" t="n">
-        <v>4447</v>
+        <v>5449</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>932</v>
+        <v>1051</v>
       </c>
       <c r="C6" t="n">
-        <v>8042</v>
+        <v>6652</v>
       </c>
       <c r="D6" t="n">
-        <v>1411</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="C7" t="n">
-        <v>4341</v>
+        <v>3735</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>669</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>1926</v>
+        <v>1730</v>
       </c>
       <c r="D8" t="n">
-        <v>392</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>613</v>
+        <v>558</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3131,7 +3131,7 @@
         <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2102</v>
+        <v>1979</v>
       </c>
       <c r="C2" t="n">
-        <v>4137</v>
+        <v>2952</v>
       </c>
       <c r="D2" t="n">
-        <v>11323</v>
+        <v>12464</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2414</v>
+        <v>2410</v>
       </c>
       <c r="C3" t="n">
-        <v>5687</v>
+        <v>3455</v>
       </c>
       <c r="D3" t="n">
-        <v>13823</v>
+        <v>14510</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2473</v>
+        <v>2812</v>
       </c>
       <c r="C4" t="n">
-        <v>7453</v>
+        <v>5171</v>
       </c>
       <c r="D4" t="n">
-        <v>10901</v>
+        <v>12242</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2057</v>
+        <v>2348</v>
       </c>
       <c r="C5" t="n">
-        <v>9922</v>
+        <v>7645</v>
       </c>
       <c r="D5" t="n">
-        <v>5051</v>
+        <v>6021</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1077</v>
+        <v>1254</v>
       </c>
       <c r="C6" t="n">
-        <v>9076</v>
+        <v>7419</v>
       </c>
       <c r="D6" t="n">
-        <v>1655</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>229</v>
+        <v>259</v>
       </c>
       <c r="C7" t="n">
-        <v>5471</v>
+        <v>4704</v>
       </c>
       <c r="D7" t="n">
-        <v>665</v>
+        <v>744</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>2468</v>
+        <v>2223</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>667</v>
+        <v>651</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4026</v>
+        <v>2701</v>
       </c>
       <c r="C2" t="n">
-        <v>14623</v>
+        <v>15834</v>
       </c>
       <c r="D2" t="n">
-        <v>19252</v>
+        <v>11261</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1946</v>
+        <v>1899</v>
       </c>
       <c r="C3" t="n">
-        <v>4556</v>
+        <v>2896</v>
       </c>
       <c r="D3" t="n">
-        <v>12680</v>
+        <v>13335</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2153</v>
+        <v>2344</v>
       </c>
       <c r="C4" t="n">
-        <v>6585</v>
+        <v>4338</v>
       </c>
       <c r="D4" t="n">
-        <v>10962</v>
+        <v>12196</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2002</v>
+        <v>2287</v>
       </c>
       <c r="C5" t="n">
-        <v>8767</v>
+        <v>6488</v>
       </c>
       <c r="D5" t="n">
-        <v>5579</v>
+        <v>6674</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1287</v>
+        <v>1506</v>
       </c>
       <c r="C6" t="n">
-        <v>9312</v>
+        <v>7443</v>
       </c>
       <c r="D6" t="n">
-        <v>2057</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>421</v>
+        <v>503</v>
       </c>
       <c r="C7" t="n">
-        <v>6794</v>
+        <v>5713</v>
       </c>
       <c r="D7" t="n">
-        <v>774</v>
+        <v>892</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="C8" t="n">
-        <v>3438</v>
+        <v>3119</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1220</v>
+        <v>1165</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4685</v>
+        <v>4289</v>
       </c>
       <c r="C2" t="n">
-        <v>10776</v>
+        <v>4768</v>
       </c>
       <c r="D2" t="n">
-        <v>3298</v>
+        <v>4901</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2970</v>
+        <v>1934</v>
       </c>
       <c r="C2" t="n">
-        <v>8657</v>
+        <v>9120</v>
       </c>
       <c r="D2" t="n">
-        <v>14323</v>
+        <v>8288</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2649</v>
+        <v>2614</v>
       </c>
       <c r="C3" t="n">
-        <v>7191</v>
+        <v>6048</v>
       </c>
       <c r="D3" t="n">
-        <v>14092</v>
+        <v>14341</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2950</v>
+        <v>3287</v>
       </c>
       <c r="C4" t="n">
-        <v>9490</v>
+        <v>6497</v>
       </c>
       <c r="D4" t="n">
-        <v>11074</v>
+        <v>12490</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1189</v>
+        <v>1454</v>
       </c>
       <c r="C5" t="n">
-        <v>13044</v>
+        <v>10008</v>
       </c>
       <c r="D5" t="n">
-        <v>4991</v>
+        <v>6047</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>389</v>
+        <v>464</v>
       </c>
       <c r="C6" t="n">
-        <v>8209</v>
+        <v>7057</v>
       </c>
       <c r="D6" t="n">
-        <v>1655</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C7" t="n">
-        <v>3369</v>
+        <v>3056</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1195</v>
+        <v>1141</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5703</v>
+        <v>5892</v>
       </c>
       <c r="C2" t="n">
-        <v>5919</v>
+        <v>9557</v>
       </c>
       <c r="D2" t="n">
-        <v>8862</v>
+        <v>22538</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1992</v>
+        <v>1824</v>
       </c>
       <c r="C3" t="n">
-        <v>5517</v>
+        <v>2441</v>
       </c>
       <c r="D3" t="n">
-        <v>1193</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4678</v>
+        <v>4365</v>
       </c>
       <c r="C2" t="n">
-        <v>6031</v>
+        <v>5627</v>
       </c>
       <c r="D2" t="n">
-        <v>14282</v>
+        <v>22002</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3158</v>
+        <v>3165</v>
       </c>
       <c r="C3" t="n">
-        <v>5001</v>
+        <v>5577</v>
       </c>
       <c r="D3" t="n">
-        <v>2393</v>
+        <v>4924</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>899</v>
+        <v>826</v>
       </c>
       <c r="C4" t="n">
-        <v>3274</v>
+        <v>1473</v>
       </c>
       <c r="D4" t="n">
-        <v>1421</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="5">
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,7 +4977,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
@@ -4991,10 +4991,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
         <v>146</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4003</v>
+        <v>4167</v>
       </c>
       <c r="C2" t="n">
-        <v>6377</v>
+        <v>5132</v>
       </c>
       <c r="D2" t="n">
-        <v>19453</v>
+        <v>28141</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3205</v>
+        <v>3086</v>
       </c>
       <c r="C3" t="n">
-        <v>4815</v>
+        <v>4851</v>
       </c>
       <c r="D3" t="n">
-        <v>4122</v>
+        <v>7301</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1716</v>
+        <v>1687</v>
       </c>
       <c r="C4" t="n">
-        <v>4184</v>
+        <v>3766</v>
       </c>
       <c r="D4" t="n">
-        <v>1564</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="C5" t="n">
-        <v>1886</v>
+        <v>898</v>
       </c>
       <c r="D5" t="n">
-        <v>1181</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
         <v>910</v>
@@ -5218,7 +5218,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
         <v>358</v>
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
         <v>372</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5288,7 +5288,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>116</v>
@@ -5302,7 +5302,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>90</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6110</v>
+        <v>5653</v>
       </c>
       <c r="C2" t="n">
-        <v>7574</v>
+        <v>8130</v>
       </c>
       <c r="D2" t="n">
-        <v>18744</v>
+        <v>26009</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2952</v>
+        <v>2960</v>
       </c>
       <c r="C3" t="n">
-        <v>4890</v>
+        <v>4348</v>
       </c>
       <c r="D3" t="n">
-        <v>6162</v>
+        <v>9954</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2087</v>
+        <v>2026</v>
       </c>
       <c r="C4" t="n">
-        <v>4436</v>
+        <v>4234</v>
       </c>
       <c r="D4" t="n">
-        <v>1983</v>
+        <v>2983</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>880</v>
+        <v>853</v>
       </c>
       <c r="C5" t="n">
-        <v>3019</v>
+        <v>2393</v>
       </c>
       <c r="D5" t="n">
-        <v>1199</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="C6" t="n">
-        <v>1104</v>
+        <v>602</v>
       </c>
       <c r="D6" t="n">
-        <v>944</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7">
@@ -5518,7 +5518,7 @@
         <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
         <v>659</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
         <v>484</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
         <v>378</v>
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5574,7 +5574,7 @@
         <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,7 +5588,7 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
         <v>216</v>
@@ -5613,7 +5613,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>99</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5806</v>
+        <v>7940</v>
       </c>
       <c r="C2" t="n">
-        <v>13509</v>
+        <v>8045</v>
       </c>
       <c r="D2" t="n">
-        <v>19720</v>
+        <v>23416</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3248</v>
+        <v>3093</v>
       </c>
       <c r="C3" t="n">
-        <v>5129</v>
+        <v>5145</v>
       </c>
       <c r="D3" t="n">
-        <v>7188</v>
+        <v>11001</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1554</v>
+        <v>1537</v>
       </c>
       <c r="C4" t="n">
-        <v>3805</v>
+        <v>3487</v>
       </c>
       <c r="D4" t="n">
-        <v>2343</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>775</v>
+        <v>747</v>
       </c>
       <c r="C5" t="n">
-        <v>2751</v>
+        <v>2460</v>
       </c>
       <c r="D5" t="n">
-        <v>1042</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C6" t="n">
-        <v>1394</v>
+        <v>1013</v>
       </c>
       <c r="D6" t="n">
-        <v>751</v>
+        <v>765</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>458</v>
+        <v>301</v>
       </c>
       <c r="D7" t="n">
         <v>512</v>
@@ -5840,10 +5840,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
         <v>364</v>
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
         <v>270</v>
@@ -5871,7 +5871,7 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
         <v>148</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4439</v>
+        <v>6507</v>
       </c>
       <c r="C2" t="n">
-        <v>10380</v>
+        <v>6814</v>
       </c>
       <c r="D2" t="n">
-        <v>29712</v>
+        <v>29721</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3762</v>
+        <v>4605</v>
       </c>
       <c r="C3" t="n">
-        <v>8689</v>
+        <v>5897</v>
       </c>
       <c r="D3" t="n">
-        <v>8853</v>
+        <v>12464</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2115</v>
+        <v>2038</v>
       </c>
       <c r="C4" t="n">
-        <v>4539</v>
+        <v>4433</v>
       </c>
       <c r="D4" t="n">
-        <v>3295</v>
+        <v>4973</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1033</v>
+        <v>1012</v>
       </c>
       <c r="C5" t="n">
-        <v>3321</v>
+        <v>3020</v>
       </c>
       <c r="D5" t="n">
-        <v>1272</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="C6" t="n">
-        <v>2158</v>
+        <v>1833</v>
       </c>
       <c r="D6" t="n">
-        <v>788</v>
+        <v>838</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>989</v>
+        <v>705</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>351</v>
+        <v>266</v>
       </c>
       <c r="D8" t="n">
         <v>387</v>
@@ -6168,7 +6168,7 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D9" t="n">
         <v>281</v>
@@ -6182,7 +6182,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
         <v>240</v>
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>120</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5168</v>
+        <v>4958</v>
       </c>
       <c r="C2" t="n">
-        <v>10335</v>
+        <v>8389</v>
       </c>
       <c r="D2" t="n">
-        <v>33593</v>
+        <v>26508</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3374</v>
+        <v>4551</v>
       </c>
       <c r="C3" t="n">
-        <v>8319</v>
+        <v>5537</v>
       </c>
       <c r="D3" t="n">
-        <v>11553</v>
+        <v>14327</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2525</v>
+        <v>2825</v>
       </c>
       <c r="C4" t="n">
-        <v>6795</v>
+        <v>5170</v>
       </c>
       <c r="D4" t="n">
-        <v>4261</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1362</v>
+        <v>1338</v>
       </c>
       <c r="C5" t="n">
-        <v>3918</v>
+        <v>3730</v>
       </c>
       <c r="D5" t="n">
-        <v>1590</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>690</v>
+        <v>668</v>
       </c>
       <c r="C6" t="n">
-        <v>2726</v>
+        <v>2420</v>
       </c>
       <c r="D6" t="n">
-        <v>865</v>
+        <v>981</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C7" t="n">
-        <v>1607</v>
+        <v>1301</v>
       </c>
       <c r="D7" t="n">
-        <v>583</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>675</v>
+        <v>489</v>
       </c>
       <c r="D8" t="n">
         <v>412</v>
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>279</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
         <v>295</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>241</v>
@@ -6507,7 +6507,7 @@
         <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -6524,7 +6524,7 @@
         <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">

--- a/output/yearly_population_iteration_37_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_37_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6173</v>
+        <v>4636</v>
       </c>
       <c r="C2" t="n">
-        <v>7404</v>
+        <v>6015</v>
       </c>
       <c r="D2" t="n">
-        <v>26782</v>
+        <v>23546</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3917</v>
+        <v>2895</v>
       </c>
       <c r="C3" t="n">
-        <v>6069</v>
+        <v>6544</v>
       </c>
       <c r="D3" t="n">
-        <v>15095</v>
+        <v>13050</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3092</v>
+        <v>2406</v>
       </c>
       <c r="C4" t="n">
-        <v>5203</v>
+        <v>5925</v>
       </c>
       <c r="D4" t="n">
-        <v>7403</v>
+        <v>6530</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1776</v>
+        <v>1594</v>
       </c>
       <c r="C5" t="n">
-        <v>4385</v>
+        <v>4360</v>
       </c>
       <c r="D5" t="n">
-        <v>2850</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>883</v>
+        <v>917</v>
       </c>
       <c r="C6" t="n">
-        <v>3012</v>
+        <v>3256</v>
       </c>
       <c r="D6" t="n">
-        <v>1160</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>407</v>
+        <v>436</v>
       </c>
       <c r="C7" t="n">
-        <v>1848</v>
+        <v>2196</v>
       </c>
       <c r="D7" t="n">
-        <v>652</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C8" t="n">
-        <v>870</v>
+        <v>1111</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>348</v>
+        <v>464</v>
       </c>
       <c r="D9" t="n">
         <v>310</v>
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
         <v>244</v>
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5986</v>
+        <v>6672</v>
       </c>
       <c r="C2" t="n">
-        <v>12176</v>
+        <v>13135</v>
       </c>
       <c r="D2" t="n">
-        <v>24594</v>
+        <v>24294</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4009</v>
+        <v>2975</v>
       </c>
       <c r="C3" t="n">
-        <v>5874</v>
+        <v>5561</v>
       </c>
       <c r="D3" t="n">
-        <v>15670</v>
+        <v>13600</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2982</v>
+        <v>2241</v>
       </c>
       <c r="C4" t="n">
-        <v>5510</v>
+        <v>6036</v>
       </c>
       <c r="D4" t="n">
-        <v>8433</v>
+        <v>7395</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2054</v>
+        <v>1718</v>
       </c>
       <c r="C5" t="n">
-        <v>4628</v>
+        <v>4990</v>
       </c>
       <c r="D5" t="n">
-        <v>3435</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1145</v>
+        <v>1108</v>
       </c>
       <c r="C6" t="n">
-        <v>3601</v>
+        <v>3680</v>
       </c>
       <c r="D6" t="n">
-        <v>1404</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>550</v>
+        <v>571</v>
       </c>
       <c r="C7" t="n">
-        <v>2342</v>
+        <v>2641</v>
       </c>
       <c r="D7" t="n">
-        <v>713</v>
+        <v>720</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="C8" t="n">
-        <v>1291</v>
+        <v>1578</v>
       </c>
       <c r="D8" t="n">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C9" t="n">
-        <v>559</v>
+        <v>725</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1206,7 +1206,7 @@
         <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>265</v>
+        <v>322</v>
       </c>
       <c r="D10" t="n">
         <v>250</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7503</v>
+        <v>7119</v>
       </c>
       <c r="C2" t="n">
-        <v>10145</v>
+        <v>11005</v>
       </c>
       <c r="D2" t="n">
-        <v>29327</v>
+        <v>30824</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3937</v>
+        <v>3625</v>
       </c>
       <c r="C3" t="n">
-        <v>7525</v>
+        <v>7664</v>
       </c>
       <c r="D3" t="n">
-        <v>15934</v>
+        <v>14012</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2898</v>
+        <v>2159</v>
       </c>
       <c r="C4" t="n">
-        <v>5556</v>
+        <v>5647</v>
       </c>
       <c r="D4" t="n">
-        <v>9137</v>
+        <v>7992</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2154</v>
+        <v>1719</v>
       </c>
       <c r="C5" t="n">
-        <v>4859</v>
+        <v>5328</v>
       </c>
       <c r="D5" t="n">
-        <v>4017</v>
+        <v>3639</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1381</v>
+        <v>1231</v>
       </c>
       <c r="C6" t="n">
-        <v>3992</v>
+        <v>4139</v>
       </c>
       <c r="D6" t="n">
-        <v>1677</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C7" t="n">
-        <v>2823</v>
+        <v>3031</v>
       </c>
       <c r="D7" t="n">
-        <v>793</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="C8" t="n">
-        <v>1689</v>
+        <v>1994</v>
       </c>
       <c r="D8" t="n">
-        <v>489</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C9" t="n">
-        <v>838</v>
+        <v>1035</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
@@ -1517,7 +1517,7 @@
         <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>368</v>
+        <v>464</v>
       </c>
       <c r="D10" t="n">
         <v>256</v>
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1542,7 +1542,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
         <v>155</v>
@@ -1559,7 +1559,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
         <v>126</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1632,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6883</v>
+        <v>6505</v>
       </c>
       <c r="C2" t="n">
-        <v>6898</v>
+        <v>7571</v>
       </c>
       <c r="D2" t="n">
-        <v>24073</v>
+        <v>25331</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4951</v>
+        <v>4124</v>
       </c>
       <c r="C3" t="n">
-        <v>10734</v>
+        <v>10921</v>
       </c>
       <c r="D3" t="n">
-        <v>17491</v>
+        <v>15234</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1990</v>
+        <v>1588</v>
       </c>
       <c r="C4" t="n">
-        <v>7704</v>
+        <v>8204</v>
       </c>
       <c r="D4" t="n">
-        <v>8741</v>
+        <v>7732</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1276</v>
+        <v>1137</v>
       </c>
       <c r="C5" t="n">
-        <v>3912</v>
+        <v>4056</v>
       </c>
       <c r="D5" t="n">
-        <v>2723</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C6" t="n">
-        <v>2766</v>
+        <v>2970</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C7" t="n">
-        <v>1655</v>
+        <v>1954</v>
       </c>
       <c r="D7" t="n">
-        <v>479</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C8" t="n">
-        <v>821</v>
+        <v>1014</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -1814,7 +1814,7 @@
         <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>360</v>
+        <v>454</v>
       </c>
       <c r="D9" t="n">
         <v>250</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1839,7 +1839,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
         <v>151</v>
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>123</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
         <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1929,7 +1929,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4146</v>
+        <v>3821</v>
       </c>
       <c r="C2" t="n">
-        <v>3278</v>
+        <v>3520</v>
       </c>
       <c r="D2" t="n">
-        <v>16520</v>
+        <v>18338</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4986</v>
+        <v>4400</v>
       </c>
       <c r="C3" t="n">
-        <v>8172</v>
+        <v>8540</v>
       </c>
       <c r="D3" t="n">
-        <v>17378</v>
+        <v>15875</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2705</v>
+        <v>2209</v>
       </c>
       <c r="C4" t="n">
-        <v>9161</v>
+        <v>9600</v>
       </c>
       <c r="D4" t="n">
-        <v>9987</v>
+        <v>8651</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1449</v>
+        <v>1252</v>
       </c>
       <c r="C5" t="n">
-        <v>5583</v>
+        <v>5799</v>
       </c>
       <c r="D5" t="n">
-        <v>3443</v>
+        <v>3135</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>779</v>
+        <v>767</v>
       </c>
       <c r="C6" t="n">
-        <v>3303</v>
+        <v>3526</v>
       </c>
       <c r="D6" t="n">
-        <v>977</v>
+        <v>963</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C7" t="n">
-        <v>2105</v>
+        <v>2394</v>
       </c>
       <c r="D7" t="n">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>1080</v>
+        <v>1305</v>
       </c>
       <c r="D8" t="n">
-        <v>338</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>408</v>
+        <v>501</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
         <v>167</v>
@@ -2164,7 +2164,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
         <v>96</v>
@@ -2184,7 +2184,7 @@
         <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2226,7 +2226,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4054</v>
+        <v>4602</v>
       </c>
       <c r="C2" t="n">
-        <v>4650</v>
+        <v>4997</v>
       </c>
       <c r="D2" t="n">
-        <v>21402</v>
+        <v>19004</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3932</v>
+        <v>3495</v>
       </c>
       <c r="C3" t="n">
-        <v>5207</v>
+        <v>5453</v>
       </c>
       <c r="D3" t="n">
-        <v>16093</v>
+        <v>15143</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3147</v>
+        <v>2703</v>
       </c>
       <c r="C4" t="n">
-        <v>8486</v>
+        <v>8881</v>
       </c>
       <c r="D4" t="n">
-        <v>10889</v>
+        <v>9566</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1755</v>
+        <v>1467</v>
       </c>
       <c r="C5" t="n">
-        <v>7149</v>
+        <v>7522</v>
       </c>
       <c r="D5" t="n">
-        <v>4343</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>971</v>
+        <v>886</v>
       </c>
       <c r="C6" t="n">
-        <v>4331</v>
+        <v>4495</v>
       </c>
       <c r="D6" t="n">
-        <v>1319</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C7" t="n">
-        <v>2641</v>
+        <v>2904</v>
       </c>
       <c r="D7" t="n">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C8" t="n">
-        <v>1501</v>
+        <v>1754</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>662</v>
+        <v>805</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>292</v>
+        <v>335</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
         <v>170</v>
@@ -2475,7 +2475,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
         <v>117</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
         <v>63</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2579,7 +2579,7 @@
         <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2417</v>
+        <v>2736</v>
       </c>
       <c r="C2" t="n">
-        <v>2179</v>
+        <v>2368</v>
       </c>
       <c r="D2" t="n">
-        <v>14951</v>
+        <v>13260</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3855</v>
+        <v>3621</v>
       </c>
       <c r="C3" t="n">
-        <v>4861</v>
+        <v>5134</v>
       </c>
       <c r="D3" t="n">
-        <v>16284</v>
+        <v>15205</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3441</v>
+        <v>2974</v>
       </c>
       <c r="C4" t="n">
-        <v>8053</v>
+        <v>8515</v>
       </c>
       <c r="D4" t="n">
-        <v>11571</v>
+        <v>10253</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1799</v>
+        <v>1529</v>
       </c>
       <c r="C5" t="n">
-        <v>8566</v>
+        <v>8914</v>
       </c>
       <c r="D5" t="n">
-        <v>4583</v>
+        <v>4104</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>771</v>
+        <v>741</v>
       </c>
       <c r="C6" t="n">
-        <v>5161</v>
+        <v>5441</v>
       </c>
       <c r="D6" t="n">
-        <v>1292</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C7" t="n">
-        <v>2774</v>
+        <v>3092</v>
       </c>
       <c r="D7" t="n">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>1104</v>
+        <v>1321</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>286</v>
+        <v>328</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
         <v>166</v>
@@ -2772,7 +2772,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
         <v>114</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2876,7 +2876,7 @@
         <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2655</v>
+        <v>2726</v>
       </c>
       <c r="C2" t="n">
-        <v>4571</v>
+        <v>5059</v>
       </c>
       <c r="D2" t="n">
-        <v>16595</v>
+        <v>16294</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2796</v>
+        <v>2779</v>
       </c>
       <c r="C3" t="n">
-        <v>3251</v>
+        <v>3460</v>
       </c>
       <c r="D3" t="n">
-        <v>15164</v>
+        <v>14064</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3157</v>
+        <v>2850</v>
       </c>
       <c r="C4" t="n">
-        <v>6383</v>
+        <v>6829</v>
       </c>
       <c r="D4" t="n">
-        <v>11943</v>
+        <v>10701</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2185</v>
+        <v>1861</v>
       </c>
       <c r="C5" t="n">
-        <v>8238</v>
+        <v>8637</v>
       </c>
       <c r="D5" t="n">
-        <v>5449</v>
+        <v>4864</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1051</v>
+        <v>937</v>
       </c>
       <c r="C6" t="n">
-        <v>6652</v>
+        <v>6879</v>
       </c>
       <c r="D6" t="n">
-        <v>1717</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C7" t="n">
-        <v>3735</v>
+        <v>4041</v>
       </c>
       <c r="D7" t="n">
-        <v>669</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8">
@@ -3044,10 +3044,10 @@
         <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>1730</v>
+        <v>2001</v>
       </c>
       <c r="D8" t="n">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>558</v>
+        <v>645</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
         <v>175</v>
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
         <v>134</v>
@@ -3103,7 +3103,7 @@
         <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1979</v>
+        <v>2001</v>
       </c>
       <c r="C2" t="n">
-        <v>2952</v>
+        <v>3012</v>
       </c>
       <c r="D2" t="n">
-        <v>12464</v>
+        <v>12063</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2410</v>
+        <v>2420</v>
       </c>
       <c r="C3" t="n">
-        <v>3455</v>
+        <v>3707</v>
       </c>
       <c r="D3" t="n">
-        <v>14510</v>
+        <v>13701</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2812</v>
+        <v>2604</v>
       </c>
       <c r="C4" t="n">
-        <v>5171</v>
+        <v>5525</v>
       </c>
       <c r="D4" t="n">
-        <v>12242</v>
+        <v>10898</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2348</v>
+        <v>2047</v>
       </c>
       <c r="C5" t="n">
-        <v>7645</v>
+        <v>8146</v>
       </c>
       <c r="D5" t="n">
-        <v>6021</v>
+        <v>5379</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1254</v>
+        <v>1092</v>
       </c>
       <c r="C6" t="n">
-        <v>7419</v>
+        <v>7693</v>
       </c>
       <c r="D6" t="n">
-        <v>2069</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>4704</v>
+        <v>4984</v>
       </c>
       <c r="D7" t="n">
-        <v>744</v>
+        <v>728</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>2223</v>
+        <v>2508</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>651</v>
+        <v>729</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
         <v>178</v>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2701</v>
+        <v>2431</v>
       </c>
       <c r="C2" t="n">
-        <v>15834</v>
+        <v>9735</v>
       </c>
       <c r="D2" t="n">
-        <v>11261</v>
+        <v>22109</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1899</v>
+        <v>1916</v>
       </c>
       <c r="C3" t="n">
-        <v>2896</v>
+        <v>3053</v>
       </c>
       <c r="D3" t="n">
-        <v>13335</v>
+        <v>12627</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2344</v>
+        <v>2208</v>
       </c>
       <c r="C4" t="n">
-        <v>4338</v>
+        <v>4642</v>
       </c>
       <c r="D4" t="n">
-        <v>12196</v>
+        <v>10970</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2287</v>
+        <v>2037</v>
       </c>
       <c r="C5" t="n">
-        <v>6488</v>
+        <v>6919</v>
       </c>
       <c r="D5" t="n">
-        <v>6674</v>
+        <v>5957</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1506</v>
+        <v>1312</v>
       </c>
       <c r="C6" t="n">
-        <v>7443</v>
+        <v>7802</v>
       </c>
       <c r="D6" t="n">
-        <v>2535</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>503</v>
+        <v>458</v>
       </c>
       <c r="C7" t="n">
-        <v>5713</v>
+        <v>6039</v>
       </c>
       <c r="D7" t="n">
-        <v>892</v>
+        <v>860</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>3119</v>
+        <v>3356</v>
       </c>
       <c r="D8" t="n">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1165</v>
+        <v>1311</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>351</v>
+        <v>383</v>
       </c>
       <c r="D10" t="n">
         <v>186</v>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
         <v>138</v>
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
         <v>94</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4289</v>
+        <v>4485</v>
       </c>
       <c r="C2" t="n">
-        <v>4768</v>
+        <v>11945</v>
       </c>
       <c r="D2" t="n">
-        <v>4901</v>
+        <v>14254</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1934</v>
+        <v>1759</v>
       </c>
       <c r="C2" t="n">
-        <v>9120</v>
+        <v>5607</v>
       </c>
       <c r="D2" t="n">
-        <v>8288</v>
+        <v>16449</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2614</v>
+        <v>2541</v>
       </c>
       <c r="C3" t="n">
-        <v>6048</v>
+        <v>4818</v>
       </c>
       <c r="D3" t="n">
-        <v>14341</v>
+        <v>14097</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3287</v>
+        <v>3010</v>
       </c>
       <c r="C4" t="n">
-        <v>6497</v>
+        <v>6941</v>
       </c>
       <c r="D4" t="n">
-        <v>12490</v>
+        <v>11223</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1454</v>
+        <v>1249</v>
       </c>
       <c r="C5" t="n">
-        <v>10008</v>
+        <v>10643</v>
       </c>
       <c r="D5" t="n">
-        <v>6047</v>
+        <v>5428</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>464</v>
+        <v>423</v>
       </c>
       <c r="C6" t="n">
-        <v>7057</v>
+        <v>7370</v>
       </c>
       <c r="D6" t="n">
-        <v>2002</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C7" t="n">
-        <v>3056</v>
+        <v>3288</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>539</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1141</v>
+        <v>1284</v>
       </c>
       <c r="D8" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>375</v>
       </c>
       <c r="D9" t="n">
         <v>182</v>
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D10" t="n">
         <v>135</v>
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D11" t="n">
         <v>92</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5892</v>
+        <v>6794</v>
       </c>
       <c r="C2" t="n">
-        <v>9557</v>
+        <v>5375</v>
       </c>
       <c r="D2" t="n">
-        <v>22538</v>
+        <v>14173</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1824</v>
+        <v>1907</v>
       </c>
       <c r="C3" t="n">
-        <v>2441</v>
+        <v>6020</v>
       </c>
       <c r="D3" t="n">
-        <v>1501</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4365</v>
+        <v>4631</v>
       </c>
       <c r="C2" t="n">
-        <v>5627</v>
+        <v>6689</v>
       </c>
       <c r="D2" t="n">
-        <v>22002</v>
+        <v>16822</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3165</v>
+        <v>3568</v>
       </c>
       <c r="C3" t="n">
-        <v>5577</v>
+        <v>4876</v>
       </c>
       <c r="D3" t="n">
-        <v>4924</v>
+        <v>4682</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>826</v>
+        <v>862</v>
       </c>
       <c r="C4" t="n">
-        <v>1473</v>
+        <v>3571</v>
       </c>
       <c r="D4" t="n">
-        <v>1483</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,7 +4977,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
@@ -4991,10 +4991,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>146</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4167</v>
+        <v>4372</v>
       </c>
       <c r="C2" t="n">
-        <v>5132</v>
+        <v>6444</v>
       </c>
       <c r="D2" t="n">
-        <v>28141</v>
+        <v>19580</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3086</v>
+        <v>3365</v>
       </c>
       <c r="C3" t="n">
-        <v>4851</v>
+        <v>5123</v>
       </c>
       <c r="D3" t="n">
-        <v>7301</v>
+        <v>6287</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1687</v>
+        <v>1878</v>
       </c>
       <c r="C4" t="n">
-        <v>3766</v>
+        <v>4189</v>
       </c>
       <c r="D4" t="n">
-        <v>2098</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="C5" t="n">
-        <v>898</v>
+        <v>2051</v>
       </c>
       <c r="D5" t="n">
-        <v>1192</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -5302,10 +5302,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5653</v>
+        <v>4919</v>
       </c>
       <c r="C2" t="n">
-        <v>8130</v>
+        <v>5939</v>
       </c>
       <c r="D2" t="n">
-        <v>26009</v>
+        <v>24540</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2960</v>
+        <v>3157</v>
       </c>
       <c r="C3" t="n">
-        <v>4348</v>
+        <v>5050</v>
       </c>
       <c r="D3" t="n">
-        <v>9954</v>
+        <v>7864</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2026</v>
+        <v>2198</v>
       </c>
       <c r="C4" t="n">
-        <v>4234</v>
+        <v>4603</v>
       </c>
       <c r="D4" t="n">
-        <v>2983</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>853</v>
+        <v>934</v>
       </c>
       <c r="C5" t="n">
-        <v>2393</v>
+        <v>3116</v>
       </c>
       <c r="D5" t="n">
-        <v>1300</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="6">
@@ -5504,10 +5504,10 @@
         <v>241</v>
       </c>
       <c r="C6" t="n">
-        <v>602</v>
+        <v>1170</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>955</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5613,10 +5613,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7940</v>
+        <v>5713</v>
       </c>
       <c r="C2" t="n">
-        <v>8045</v>
+        <v>9122</v>
       </c>
       <c r="D2" t="n">
-        <v>23416</v>
+        <v>26548</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3093</v>
+        <v>2916</v>
       </c>
       <c r="C3" t="n">
-        <v>5145</v>
+        <v>4505</v>
       </c>
       <c r="D3" t="n">
-        <v>11001</v>
+        <v>9262</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1537</v>
+        <v>1663</v>
       </c>
       <c r="C4" t="n">
-        <v>3487</v>
+        <v>3929</v>
       </c>
       <c r="D4" t="n">
-        <v>3634</v>
+        <v>3277</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>747</v>
+        <v>806</v>
       </c>
       <c r="C5" t="n">
-        <v>2460</v>
+        <v>2836</v>
       </c>
       <c r="D5" t="n">
-        <v>1246</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="C6" t="n">
-        <v>1013</v>
+        <v>1428</v>
       </c>
       <c r="D6" t="n">
-        <v>765</v>
+        <v>782</v>
       </c>
     </row>
     <row r="7">
@@ -5829,10 +5829,10 @@
         <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>301</v>
+        <v>480</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
         <v>270</v>
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6507</v>
+        <v>4348</v>
       </c>
       <c r="C2" t="n">
-        <v>6814</v>
+        <v>9168</v>
       </c>
       <c r="D2" t="n">
-        <v>29721</v>
+        <v>21968</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4605</v>
+        <v>3569</v>
       </c>
       <c r="C3" t="n">
-        <v>5897</v>
+        <v>6197</v>
       </c>
       <c r="D3" t="n">
-        <v>12464</v>
+        <v>11484</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2038</v>
+        <v>1986</v>
       </c>
       <c r="C4" t="n">
-        <v>4433</v>
+        <v>4195</v>
       </c>
       <c r="D4" t="n">
-        <v>4973</v>
+        <v>4352</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1012</v>
+        <v>1102</v>
       </c>
       <c r="C5" t="n">
-        <v>3020</v>
+        <v>3417</v>
       </c>
       <c r="D5" t="n">
-        <v>1689</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>470</v>
+        <v>497</v>
       </c>
       <c r="C6" t="n">
-        <v>1833</v>
+        <v>2208</v>
       </c>
       <c r="D6" t="n">
-        <v>838</v>
+        <v>869</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C7" t="n">
-        <v>705</v>
+        <v>1009</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>266</v>
+        <v>357</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6266,10 +6266,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4958</v>
+        <v>3805</v>
       </c>
       <c r="C2" t="n">
-        <v>8389</v>
+        <v>8173</v>
       </c>
       <c r="D2" t="n">
-        <v>26508</v>
+        <v>23204</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4551</v>
+        <v>3255</v>
       </c>
       <c r="C3" t="n">
-        <v>5537</v>
+        <v>6825</v>
       </c>
       <c r="D3" t="n">
-        <v>14327</v>
+        <v>12334</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2825</v>
+        <v>2386</v>
       </c>
       <c r="C4" t="n">
-        <v>5170</v>
+        <v>5182</v>
       </c>
       <c r="D4" t="n">
-        <v>6260</v>
+        <v>5589</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1338</v>
+        <v>1345</v>
       </c>
       <c r="C5" t="n">
-        <v>3730</v>
+        <v>3771</v>
       </c>
       <c r="D5" t="n">
-        <v>2220</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>668</v>
+        <v>725</v>
       </c>
       <c r="C6" t="n">
-        <v>2420</v>
+        <v>2821</v>
       </c>
       <c r="D6" t="n">
-        <v>981</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="C7" t="n">
-        <v>1301</v>
+        <v>1621</v>
       </c>
       <c r="D7" t="n">
-        <v>594</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>489</v>
+        <v>689</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>238</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
         <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_37_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_37_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4636</v>
+        <v>1286</v>
       </c>
       <c r="C2" t="n">
-        <v>6015</v>
+        <v>1741</v>
       </c>
       <c r="D2" t="n">
-        <v>23546</v>
+        <v>7786</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2895</v>
+        <v>1966</v>
       </c>
       <c r="C3" t="n">
-        <v>6544</v>
+        <v>5378</v>
       </c>
       <c r="D3" t="n">
-        <v>13050</v>
+        <v>9713</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2406</v>
+        <v>1099</v>
       </c>
       <c r="C4" t="n">
-        <v>5925</v>
+        <v>7585</v>
       </c>
       <c r="D4" t="n">
-        <v>6530</v>
+        <v>5216</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1594</v>
+        <v>442</v>
       </c>
       <c r="C5" t="n">
-        <v>4360</v>
+        <v>4336</v>
       </c>
       <c r="D5" t="n">
-        <v>2623</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>917</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>3256</v>
+        <v>1545</v>
       </c>
       <c r="D6" t="n">
-        <v>1152</v>
+        <v>743</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>436</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>2196</v>
+        <v>650</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>161</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>1111</v>
+        <v>350</v>
       </c>
       <c r="D8" t="n">
-        <v>427</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>464</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6672</v>
+        <v>988</v>
       </c>
       <c r="C2" t="n">
-        <v>13135</v>
+        <v>8475</v>
       </c>
       <c r="D2" t="n">
-        <v>24294</v>
+        <v>11046</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2975</v>
+        <v>1375</v>
       </c>
       <c r="C3" t="n">
-        <v>5561</v>
+        <v>2952</v>
       </c>
       <c r="D3" t="n">
-        <v>13600</v>
+        <v>8705</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2241</v>
+        <v>1319</v>
       </c>
       <c r="C4" t="n">
-        <v>6036</v>
+        <v>6250</v>
       </c>
       <c r="D4" t="n">
-        <v>7395</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1718</v>
+        <v>658</v>
       </c>
       <c r="C5" t="n">
-        <v>4990</v>
+        <v>5992</v>
       </c>
       <c r="D5" t="n">
-        <v>3118</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1108</v>
+        <v>286</v>
       </c>
       <c r="C6" t="n">
-        <v>3680</v>
+        <v>2989</v>
       </c>
       <c r="D6" t="n">
-        <v>1362</v>
+        <v>921</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>571</v>
+        <v>129</v>
       </c>
       <c r="C7" t="n">
-        <v>2641</v>
+        <v>1103</v>
       </c>
       <c r="D7" t="n">
-        <v>720</v>
+        <v>540</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>241</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1578</v>
+        <v>497</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>725</v>
+        <v>319</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>322</v>
+        <v>251</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7119</v>
+        <v>508</v>
       </c>
       <c r="C2" t="n">
-        <v>11005</v>
+        <v>3357</v>
       </c>
       <c r="D2" t="n">
-        <v>30824</v>
+        <v>7457</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3625</v>
+        <v>1210</v>
       </c>
       <c r="C3" t="n">
-        <v>7664</v>
+        <v>5073</v>
       </c>
       <c r="D3" t="n">
-        <v>14012</v>
+        <v>8767</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2159</v>
+        <v>1454</v>
       </c>
       <c r="C4" t="n">
-        <v>5647</v>
+        <v>5418</v>
       </c>
       <c r="D4" t="n">
-        <v>7992</v>
+        <v>6345</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1719</v>
+        <v>655</v>
       </c>
       <c r="C5" t="n">
-        <v>5328</v>
+        <v>6746</v>
       </c>
       <c r="D5" t="n">
-        <v>3639</v>
+        <v>2711</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1231</v>
+        <v>248</v>
       </c>
       <c r="C6" t="n">
-        <v>4139</v>
+        <v>4004</v>
       </c>
       <c r="D6" t="n">
-        <v>1566</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>701</v>
+        <v>75</v>
       </c>
       <c r="C7" t="n">
-        <v>3031</v>
+        <v>1112</v>
       </c>
       <c r="D7" t="n">
-        <v>800</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>325</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1994</v>
+        <v>497</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>1035</v>
+        <v>245</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>464</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>234</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6505</v>
+        <v>720</v>
       </c>
       <c r="C2" t="n">
-        <v>7571</v>
+        <v>2945</v>
       </c>
       <c r="D2" t="n">
-        <v>25331</v>
+        <v>13178</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4124</v>
+        <v>751</v>
       </c>
       <c r="C3" t="n">
-        <v>10921</v>
+        <v>3651</v>
       </c>
       <c r="D3" t="n">
-        <v>15234</v>
+        <v>8010</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1588</v>
+        <v>1192</v>
       </c>
       <c r="C4" t="n">
-        <v>8204</v>
+        <v>5168</v>
       </c>
       <c r="D4" t="n">
-        <v>7732</v>
+        <v>6593</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1137</v>
+        <v>895</v>
       </c>
       <c r="C5" t="n">
-        <v>4056</v>
+        <v>5982</v>
       </c>
       <c r="D5" t="n">
-        <v>2512</v>
+        <v>3256</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>647</v>
+        <v>383</v>
       </c>
       <c r="C6" t="n">
-        <v>2970</v>
+        <v>5382</v>
       </c>
       <c r="D6" t="n">
-        <v>784</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>300</v>
+        <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>1954</v>
+        <v>2465</v>
       </c>
       <c r="D7" t="n">
-        <v>471</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>1014</v>
+        <v>765</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>454</v>
+        <v>348</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3821</v>
+        <v>499</v>
       </c>
       <c r="C2" t="n">
-        <v>3520</v>
+        <v>2414</v>
       </c>
       <c r="D2" t="n">
-        <v>18338</v>
+        <v>8921</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4400</v>
+        <v>645</v>
       </c>
       <c r="C3" t="n">
-        <v>8540</v>
+        <v>2966</v>
       </c>
       <c r="D3" t="n">
-        <v>15875</v>
+        <v>8356</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2209</v>
+        <v>957</v>
       </c>
       <c r="C4" t="n">
-        <v>9600</v>
+        <v>4466</v>
       </c>
       <c r="D4" t="n">
-        <v>8651</v>
+        <v>6673</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1252</v>
+        <v>964</v>
       </c>
       <c r="C5" t="n">
-        <v>5799</v>
+        <v>5727</v>
       </c>
       <c r="D5" t="n">
-        <v>3135</v>
+        <v>3668</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>767</v>
+        <v>488</v>
       </c>
       <c r="C6" t="n">
-        <v>3526</v>
+        <v>5883</v>
       </c>
       <c r="D6" t="n">
-        <v>963</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>281</v>
+        <v>149</v>
       </c>
       <c r="C7" t="n">
-        <v>2394</v>
+        <v>3547</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>681</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>1305</v>
+        <v>1222</v>
       </c>
       <c r="D8" t="n">
-        <v>333</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>501</v>
+        <v>457</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4602</v>
+        <v>978</v>
       </c>
       <c r="C2" t="n">
-        <v>4997</v>
+        <v>11018</v>
       </c>
       <c r="D2" t="n">
-        <v>19004</v>
+        <v>12822</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3495</v>
+        <v>488</v>
       </c>
       <c r="C3" t="n">
-        <v>5453</v>
+        <v>2361</v>
       </c>
       <c r="D3" t="n">
-        <v>15143</v>
+        <v>7862</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2703</v>
+        <v>725</v>
       </c>
       <c r="C4" t="n">
-        <v>8881</v>
+        <v>3652</v>
       </c>
       <c r="D4" t="n">
-        <v>9566</v>
+        <v>6760</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1467</v>
+        <v>878</v>
       </c>
       <c r="C5" t="n">
-        <v>7522</v>
+        <v>5002</v>
       </c>
       <c r="D5" t="n">
-        <v>3886</v>
+        <v>4046</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>886</v>
+        <v>636</v>
       </c>
       <c r="C6" t="n">
-        <v>4495</v>
+        <v>5752</v>
       </c>
       <c r="D6" t="n">
-        <v>1263</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>413</v>
+        <v>248</v>
       </c>
       <c r="C7" t="n">
-        <v>2904</v>
+        <v>4633</v>
       </c>
       <c r="D7" t="n">
-        <v>575</v>
+        <v>787</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>143</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1754</v>
+        <v>2213</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>516</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>805</v>
+        <v>761</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2736</v>
+        <v>641</v>
       </c>
       <c r="C2" t="n">
-        <v>2368</v>
+        <v>5553</v>
       </c>
       <c r="D2" t="n">
-        <v>13260</v>
+        <v>9231</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3621</v>
+        <v>748</v>
       </c>
       <c r="C3" t="n">
-        <v>5134</v>
+        <v>5097</v>
       </c>
       <c r="D3" t="n">
-        <v>15205</v>
+        <v>8757</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2974</v>
+        <v>1164</v>
       </c>
       <c r="C4" t="n">
-        <v>8515</v>
+        <v>5137</v>
       </c>
       <c r="D4" t="n">
-        <v>10253</v>
+        <v>7160</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1529</v>
+        <v>660</v>
       </c>
       <c r="C5" t="n">
-        <v>8914</v>
+        <v>7716</v>
       </c>
       <c r="D5" t="n">
-        <v>4104</v>
+        <v>3863</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>741</v>
+        <v>229</v>
       </c>
       <c r="C6" t="n">
-        <v>5441</v>
+        <v>6062</v>
       </c>
       <c r="D6" t="n">
-        <v>1242</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>3092</v>
+        <v>2168</v>
       </c>
       <c r="D7" t="n">
-        <v>574</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>1321</v>
+        <v>745</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2726</v>
+        <v>298</v>
       </c>
       <c r="C2" t="n">
-        <v>5059</v>
+        <v>3091</v>
       </c>
       <c r="D2" t="n">
-        <v>16294</v>
+        <v>6660</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2779</v>
+        <v>589</v>
       </c>
       <c r="C3" t="n">
-        <v>3460</v>
+        <v>4679</v>
       </c>
       <c r="D3" t="n">
-        <v>14064</v>
+        <v>8188</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2850</v>
+        <v>810</v>
       </c>
       <c r="C4" t="n">
-        <v>6829</v>
+        <v>4861</v>
       </c>
       <c r="D4" t="n">
-        <v>10701</v>
+        <v>6938</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1861</v>
+        <v>626</v>
       </c>
       <c r="C5" t="n">
-        <v>8637</v>
+        <v>5679</v>
       </c>
       <c r="D5" t="n">
-        <v>4864</v>
+        <v>3932</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>937</v>
+        <v>234</v>
       </c>
       <c r="C6" t="n">
-        <v>6879</v>
+        <v>5667</v>
       </c>
       <c r="D6" t="n">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>281</v>
+        <v>61</v>
       </c>
       <c r="C7" t="n">
-        <v>4041</v>
+        <v>2833</v>
       </c>
       <c r="D7" t="n">
-        <v>658</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>2001</v>
+        <v>872</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>645</v>
+        <v>293</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>137</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2001</v>
+        <v>171</v>
       </c>
       <c r="C2" t="n">
-        <v>3012</v>
+        <v>4189</v>
       </c>
       <c r="D2" t="n">
-        <v>12063</v>
+        <v>14717</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2420</v>
+        <v>375</v>
       </c>
       <c r="C3" t="n">
-        <v>3707</v>
+        <v>3305</v>
       </c>
       <c r="D3" t="n">
-        <v>13701</v>
+        <v>7407</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2604</v>
+        <v>611</v>
       </c>
       <c r="C4" t="n">
-        <v>5525</v>
+        <v>4655</v>
       </c>
       <c r="D4" t="n">
-        <v>10898</v>
+        <v>6967</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2047</v>
+        <v>648</v>
       </c>
       <c r="C5" t="n">
-        <v>8146</v>
+        <v>5159</v>
       </c>
       <c r="D5" t="n">
-        <v>5379</v>
+        <v>4360</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1092</v>
+        <v>382</v>
       </c>
       <c r="C6" t="n">
-        <v>7693</v>
+        <v>5608</v>
       </c>
       <c r="D6" t="n">
-        <v>1919</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>123</v>
       </c>
       <c r="C7" t="n">
-        <v>4984</v>
+        <v>4331</v>
       </c>
       <c r="D7" t="n">
-        <v>728</v>
+        <v>763</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>2508</v>
+        <v>1841</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>729</v>
+        <v>562</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2431</v>
+        <v>188</v>
       </c>
       <c r="C2" t="n">
-        <v>9735</v>
+        <v>5132</v>
       </c>
       <c r="D2" t="n">
-        <v>22109</v>
+        <v>13211</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1916</v>
+        <v>235</v>
       </c>
       <c r="C3" t="n">
-        <v>3053</v>
+        <v>3304</v>
       </c>
       <c r="D3" t="n">
-        <v>12627</v>
+        <v>7996</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2208</v>
+        <v>438</v>
       </c>
       <c r="C4" t="n">
-        <v>4642</v>
+        <v>3800</v>
       </c>
       <c r="D4" t="n">
-        <v>10970</v>
+        <v>6835</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2037</v>
+        <v>576</v>
       </c>
       <c r="C5" t="n">
-        <v>6919</v>
+        <v>4790</v>
       </c>
       <c r="D5" t="n">
-        <v>5957</v>
+        <v>4677</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1312</v>
+        <v>459</v>
       </c>
       <c r="C6" t="n">
-        <v>7802</v>
+        <v>5323</v>
       </c>
       <c r="D6" t="n">
-        <v>2326</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>458</v>
+        <v>214</v>
       </c>
       <c r="C7" t="n">
-        <v>6039</v>
+        <v>4954</v>
       </c>
       <c r="D7" t="n">
-        <v>860</v>
+        <v>959</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>3356</v>
+        <v>3011</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>1311</v>
+        <v>1138</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4485</v>
+        <v>2216</v>
       </c>
       <c r="C2" t="n">
-        <v>11945</v>
+        <v>8242</v>
       </c>
       <c r="D2" t="n">
-        <v>14254</v>
+        <v>5133</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1759</v>
+        <v>718</v>
       </c>
       <c r="C2" t="n">
-        <v>5607</v>
+        <v>18257</v>
       </c>
       <c r="D2" t="n">
-        <v>16449</v>
+        <v>17095</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2541</v>
+        <v>179</v>
       </c>
       <c r="C3" t="n">
-        <v>4818</v>
+        <v>3679</v>
       </c>
       <c r="D3" t="n">
-        <v>14097</v>
+        <v>8167</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3010</v>
+        <v>307</v>
       </c>
       <c r="C4" t="n">
-        <v>6941</v>
+        <v>3446</v>
       </c>
       <c r="D4" t="n">
-        <v>11223</v>
+        <v>6751</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1249</v>
+        <v>473</v>
       </c>
       <c r="C5" t="n">
-        <v>10643</v>
+        <v>4224</v>
       </c>
       <c r="D5" t="n">
-        <v>5428</v>
+        <v>4887</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>423</v>
+        <v>474</v>
       </c>
       <c r="C6" t="n">
-        <v>7370</v>
+        <v>5030</v>
       </c>
       <c r="D6" t="n">
-        <v>1872</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>283</v>
       </c>
       <c r="C7" t="n">
-        <v>3288</v>
+        <v>5066</v>
       </c>
       <c r="D7" t="n">
-        <v>539</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>1284</v>
+        <v>3847</v>
       </c>
       <c r="D8" t="n">
-        <v>293</v>
+        <v>501</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>375</v>
+        <v>1908</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>157</v>
+        <v>660</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>227</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6794</v>
+        <v>3057</v>
       </c>
       <c r="C2" t="n">
-        <v>5375</v>
+        <v>5575</v>
       </c>
       <c r="D2" t="n">
-        <v>14173</v>
+        <v>16777</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1907</v>
+        <v>735</v>
       </c>
       <c r="C3" t="n">
-        <v>6020</v>
+        <v>3254</v>
       </c>
       <c r="D3" t="n">
-        <v>3034</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4631</v>
+        <v>1551</v>
       </c>
       <c r="C2" t="n">
-        <v>6689</v>
+        <v>4477</v>
       </c>
       <c r="D2" t="n">
-        <v>16822</v>
+        <v>21146</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3568</v>
+        <v>1608</v>
       </c>
       <c r="C3" t="n">
-        <v>4876</v>
+        <v>3992</v>
       </c>
       <c r="D3" t="n">
-        <v>4682</v>
+        <v>3945</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>862</v>
+        <v>367</v>
       </c>
       <c r="C4" t="n">
-        <v>3571</v>
+        <v>2078</v>
       </c>
       <c r="D4" t="n">
-        <v>1792</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4372</v>
+        <v>3004</v>
       </c>
       <c r="C2" t="n">
-        <v>6444</v>
+        <v>7733</v>
       </c>
       <c r="D2" t="n">
-        <v>19580</v>
+        <v>18199</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3365</v>
+        <v>1315</v>
       </c>
       <c r="C3" t="n">
-        <v>5123</v>
+        <v>3674</v>
       </c>
       <c r="D3" t="n">
-        <v>6287</v>
+        <v>6544</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1878</v>
+        <v>865</v>
       </c>
       <c r="C4" t="n">
-        <v>4189</v>
+        <v>3192</v>
       </c>
       <c r="D4" t="n">
-        <v>2292</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>407</v>
+        <v>205</v>
       </c>
       <c r="C5" t="n">
-        <v>2051</v>
+        <v>1297</v>
       </c>
       <c r="D5" t="n">
-        <v>1258</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>401</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4919</v>
+        <v>1991</v>
       </c>
       <c r="C2" t="n">
-        <v>5939</v>
+        <v>8402</v>
       </c>
       <c r="D2" t="n">
-        <v>24540</v>
+        <v>17403</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3157</v>
+        <v>1761</v>
       </c>
       <c r="C3" t="n">
-        <v>5050</v>
+        <v>5184</v>
       </c>
       <c r="D3" t="n">
-        <v>7864</v>
+        <v>7937</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2198</v>
+        <v>936</v>
       </c>
       <c r="C4" t="n">
-        <v>4603</v>
+        <v>3372</v>
       </c>
       <c r="D4" t="n">
-        <v>2951</v>
+        <v>2668</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>934</v>
+        <v>461</v>
       </c>
       <c r="C5" t="n">
-        <v>3116</v>
+        <v>2343</v>
       </c>
       <c r="D5" t="n">
-        <v>1386</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>241</v>
+        <v>145</v>
       </c>
       <c r="C6" t="n">
-        <v>1170</v>
+        <v>823</v>
       </c>
       <c r="D6" t="n">
-        <v>955</v>
+        <v>838</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>292</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>251</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5713</v>
+        <v>2031</v>
       </c>
       <c r="C2" t="n">
-        <v>9122</v>
+        <v>6516</v>
       </c>
       <c r="D2" t="n">
-        <v>26548</v>
+        <v>14370</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2916</v>
+        <v>1544</v>
       </c>
       <c r="C3" t="n">
-        <v>4505</v>
+        <v>5988</v>
       </c>
       <c r="D3" t="n">
-        <v>9262</v>
+        <v>8880</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1663</v>
+        <v>1150</v>
       </c>
       <c r="C4" t="n">
-        <v>3929</v>
+        <v>4310</v>
       </c>
       <c r="D4" t="n">
-        <v>3277</v>
+        <v>3598</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>806</v>
+        <v>601</v>
       </c>
       <c r="C5" t="n">
-        <v>2836</v>
+        <v>2847</v>
       </c>
       <c r="D5" t="n">
-        <v>1296</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="C6" t="n">
-        <v>1428</v>
+        <v>1601</v>
       </c>
       <c r="D6" t="n">
-        <v>782</v>
+        <v>878</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>480</v>
+        <v>562</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>220</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4348</v>
+        <v>2924</v>
       </c>
       <c r="C2" t="n">
-        <v>9168</v>
+        <v>6629</v>
       </c>
       <c r="D2" t="n">
-        <v>21968</v>
+        <v>14310</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3569</v>
+        <v>1470</v>
       </c>
       <c r="C3" t="n">
-        <v>6197</v>
+        <v>5453</v>
       </c>
       <c r="D3" t="n">
-        <v>11484</v>
+        <v>9089</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1986</v>
+        <v>1140</v>
       </c>
       <c r="C4" t="n">
-        <v>4195</v>
+        <v>5106</v>
       </c>
       <c r="D4" t="n">
-        <v>4352</v>
+        <v>4452</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1102</v>
+        <v>753</v>
       </c>
       <c r="C5" t="n">
-        <v>3417</v>
+        <v>3532</v>
       </c>
       <c r="D5" t="n">
-        <v>1655</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>497</v>
+        <v>379</v>
       </c>
       <c r="C6" t="n">
-        <v>2208</v>
+        <v>2194</v>
       </c>
       <c r="D6" t="n">
-        <v>869</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C7" t="n">
-        <v>1009</v>
+        <v>1055</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>423</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3805</v>
+        <v>2552</v>
       </c>
       <c r="C2" t="n">
-        <v>8173</v>
+        <v>3977</v>
       </c>
       <c r="D2" t="n">
-        <v>23204</v>
+        <v>11191</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3255</v>
+        <v>2010</v>
       </c>
       <c r="C3" t="n">
-        <v>6825</v>
+        <v>8178</v>
       </c>
       <c r="D3" t="n">
-        <v>12334</v>
+        <v>10178</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2386</v>
+        <v>695</v>
       </c>
       <c r="C4" t="n">
-        <v>5182</v>
+        <v>6674</v>
       </c>
       <c r="D4" t="n">
-        <v>5589</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1345</v>
+        <v>350</v>
       </c>
       <c r="C5" t="n">
-        <v>3771</v>
+        <v>2150</v>
       </c>
       <c r="D5" t="n">
-        <v>2080</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>725</v>
+        <v>152</v>
       </c>
       <c r="C6" t="n">
-        <v>2821</v>
+        <v>1033</v>
       </c>
       <c r="D6" t="n">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>288</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>1621</v>
+        <v>414</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>462</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>689</v>
+        <v>282</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>281</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
